--- a/output/yearly_benthic_cover_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_76_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.29140508847469</v>
+        <v>45.08597471511363</v>
       </c>
       <c r="M2" t="n">
-        <v>100.2201814015781</v>
+        <v>99.6719953834978</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.92214859450274</v>
+        <v>88.05808138163277</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87948619604352</v>
+        <v>45.9322808378471</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228497913756453</v>
+        <v>2.228806801814093</v>
       </c>
       <c r="E3" t="n">
-        <v>5.672500222859007</v>
+        <v>5.710123287143928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428326379188178</v>
+        <v>0.7429356006046977</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95714392217446</v>
+        <v>33.97404262469925</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17030134426562</v>
+        <v>34.17503762781609</v>
       </c>
       <c r="I3" t="n">
-        <v>6.50816856653577</v>
+        <v>6.583787935775351</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642703986992611</v>
+        <v>4.64334750377936</v>
       </c>
       <c r="K3" t="n">
-        <v>12.07785140549725</v>
+        <v>11.94191861836724</v>
       </c>
       <c r="L3" t="n">
-        <v>48.80902812754119</v>
+        <v>48.88948439721193</v>
       </c>
       <c r="M3" t="n">
-        <v>106.766365729082</v>
+        <v>106.7636838534263</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.88028241185538</v>
+        <v>87.16035460121375</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4630208149691</v>
+        <v>42.67259652492285</v>
       </c>
       <c r="D4" t="n">
-        <v>2.177560812065089</v>
+        <v>2.185654389685337</v>
       </c>
       <c r="E4" t="n">
-        <v>6.44864016235769</v>
+        <v>6.515906034958911</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744381563943316</v>
+        <v>0.7444977325868752</v>
       </c>
       <c r="G4" t="n">
-        <v>33.1809805331783</v>
+        <v>33.31626381326183</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24155194139254</v>
+        <v>34.24689569899626</v>
       </c>
       <c r="I4" t="n">
-        <v>5.434782624272713</v>
+        <v>5.498026103056579</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652384774645725</v>
+        <v>4.65311082866797</v>
       </c>
       <c r="K4" t="n">
-        <v>13.11971758814463</v>
+        <v>12.83964539878626</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2364791367047</v>
+        <v>44.30487507807491</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81921753981844</v>
+        <v>99.81711700178401</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.5519580598981</v>
+        <v>86.06680460062974</v>
       </c>
       <c r="C5" t="n">
-        <v>41.97806963962499</v>
+        <v>42.43238670644458</v>
       </c>
       <c r="D5" t="n">
-        <v>2.112101008482047</v>
+        <v>2.132555009584048</v>
       </c>
       <c r="E5" t="n">
-        <v>7.010952411966191</v>
+        <v>7.122577513731465</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745697432081211</v>
+        <v>0.745821169744045</v>
       </c>
       <c r="G5" t="n">
-        <v>32.18352482201734</v>
+        <v>32.50686184919837</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30208187573571</v>
+        <v>34.30777380822607</v>
       </c>
       <c r="I5" t="n">
-        <v>4.536991559108026</v>
+        <v>4.589832939245452</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660608950507569</v>
+        <v>4.661382310900281</v>
       </c>
       <c r="K5" t="n">
-        <v>14.44804194010192</v>
+        <v>13.93319539937027</v>
       </c>
       <c r="L5" t="n">
-        <v>43.42292223626552</v>
+        <v>43.48169494687804</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84903381599243</v>
+        <v>99.84727705269289</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83.99658325542757</v>
+        <v>84.7736701405401</v>
       </c>
       <c r="C6" t="n">
-        <v>41.12703858661905</v>
+        <v>41.85215787928571</v>
       </c>
       <c r="D6" t="n">
-        <v>2.035625322288116</v>
+        <v>2.069634382433748</v>
       </c>
       <c r="E6" t="n">
-        <v>7.388182003171477</v>
+        <v>7.550864202631494</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468179494620576</v>
+        <v>0.7469445369646909</v>
       </c>
       <c r="G6" t="n">
-        <v>31.01821258788699</v>
+        <v>31.54775311575534</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35362567525465</v>
+        <v>34.35944870037579</v>
       </c>
       <c r="I6" t="n">
-        <v>3.786507533226417</v>
+        <v>3.830621846349732</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66761218413786</v>
+        <v>4.668403356029319</v>
       </c>
       <c r="K6" t="n">
-        <v>16.00341674457243</v>
+        <v>15.22632985945991</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74351712549996</v>
+        <v>42.79401690183089</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87397245669145</v>
+        <v>99.87250464057651</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.05633440205152</v>
+        <v>83.25290333241171</v>
       </c>
       <c r="C7" t="n">
-        <v>39.77449283349181</v>
+        <v>40.9264602416499</v>
       </c>
       <c r="D7" t="n">
-        <v>1.940451328793077</v>
+        <v>1.995732266103613</v>
       </c>
       <c r="E7" t="n">
-        <v>7.5693324080433</v>
+        <v>7.81395103478104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477764580322646</v>
+        <v>0.747900434139054</v>
       </c>
       <c r="G7" t="n">
-        <v>29.56798148162968</v>
+        <v>30.42125186485648</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39771706948417</v>
+        <v>34.40341997039649</v>
       </c>
       <c r="I7" t="n">
-        <v>3.159472793367373</v>
+        <v>3.196270048765948</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673602862701653</v>
+        <v>4.674377713369088</v>
       </c>
       <c r="K7" t="n">
-        <v>17.9436655979485</v>
+        <v>16.7470966675883</v>
       </c>
       <c r="L7" t="n">
-        <v>42.17666080374786</v>
+        <v>42.22003692836321</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89481923518815</v>
+        <v>99.8935938376014</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.01041562103833</v>
+        <v>87.97877233323811</v>
       </c>
       <c r="C8" t="n">
-        <v>42.09045131334599</v>
+        <v>43.17200840372605</v>
       </c>
       <c r="D8" t="n">
-        <v>1.944667980612345</v>
+        <v>1.999933261207812</v>
       </c>
       <c r="E8" t="n">
-        <v>9.414128202813602</v>
+        <v>9.604249551167026</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494013959605601</v>
+        <v>0.749474756564767</v>
       </c>
       <c r="G8" t="n">
-        <v>30.07371739268191</v>
+        <v>30.90922745136616</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47246421418576</v>
+        <v>34.47583880197929</v>
       </c>
       <c r="I8" t="n">
-        <v>5.672277710030659</v>
+        <v>5.555831282423279</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6837587247535</v>
+        <v>4.684217228529794</v>
       </c>
       <c r="K8" t="n">
-        <v>12.98958437896165</v>
+        <v>12.02122766676188</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73129836009539</v>
+        <v>44.62195856674607</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81133405240304</v>
+        <v>99.815194637234</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84.7578901547998</v>
+        <v>85.98391080341838</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71720585444524</v>
+        <v>42.03966672415595</v>
       </c>
       <c r="D9" t="n">
-        <v>1.842368834007175</v>
+        <v>1.909517474794048</v>
       </c>
       <c r="E9" t="n">
-        <v>9.708182144890808</v>
+        <v>9.943077885713022</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507971131951163</v>
+        <v>0.7508223738085602</v>
       </c>
       <c r="G9" t="n">
-        <v>28.49169122925031</v>
+        <v>29.51183976765445</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53666720697534</v>
+        <v>34.53782919519377</v>
       </c>
       <c r="I9" t="n">
-        <v>4.735701669011562</v>
+        <v>4.638184269951038</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692481957469476</v>
+        <v>4.692639836303502</v>
       </c>
       <c r="K9" t="n">
-        <v>15.24210984520019</v>
+        <v>14.01608919658159</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88312103063148</v>
+        <v>43.78991543252848</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84243673027692</v>
+        <v>99.84567135326603</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.4004873763964</v>
+        <v>83.76874196241513</v>
       </c>
       <c r="C10" t="n">
-        <v>39.09337288585827</v>
+        <v>40.54428092068225</v>
       </c>
       <c r="D10" t="n">
-        <v>1.736675739584101</v>
+        <v>1.810041933961448</v>
       </c>
       <c r="E10" t="n">
-        <v>9.810030791711059</v>
+        <v>10.07028183320199</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519976307825789</v>
+        <v>0.7519789365049007</v>
       </c>
       <c r="G10" t="n">
-        <v>26.85717866272126</v>
+        <v>27.97443240657802</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59189101599862</v>
+        <v>34.59103107922543</v>
       </c>
       <c r="I10" t="n">
-        <v>3.952728343207669</v>
+        <v>3.871107419787726</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699985192391116</v>
+        <v>4.69986835315563</v>
       </c>
       <c r="K10" t="n">
-        <v>17.59951262360361</v>
+        <v>16.23125803758485</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17556722195445</v>
+        <v>43.09562258978981</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86845273141633</v>
+        <v>99.87116154805692</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.97633750384436</v>
+        <v>81.43069391658268</v>
       </c>
       <c r="C11" t="n">
-        <v>37.28072299991472</v>
+        <v>38.80634087271775</v>
       </c>
       <c r="D11" t="n">
-        <v>1.629289217272312</v>
+        <v>1.70611019259604</v>
       </c>
       <c r="E11" t="n">
-        <v>9.753176963165853</v>
+        <v>10.03041580011631</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530314535017884</v>
+        <v>0.752973251834731</v>
       </c>
       <c r="G11" t="n">
-        <v>25.19647773280171</v>
+        <v>26.36815388939397</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63944686108226</v>
+        <v>34.63676958439762</v>
       </c>
       <c r="I11" t="n">
-        <v>3.298468691634276</v>
+        <v>3.230188374276938</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706446584386176</v>
+        <v>4.706082823967068</v>
       </c>
       <c r="K11" t="n">
-        <v>20.02366249615562</v>
+        <v>18.5693060834173</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58581649439613</v>
+        <v>42.51682228220417</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89020199046647</v>
+        <v>99.89246923833923</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.41822532388109</v>
+        <v>78.91191927649633</v>
       </c>
       <c r="C12" t="n">
-        <v>35.23198383839424</v>
+        <v>36.78751576805982</v>
       </c>
       <c r="D12" t="n">
-        <v>1.517142021994429</v>
+        <v>1.595147608722159</v>
       </c>
       <c r="E12" t="n">
-        <v>9.540510004465517</v>
+        <v>9.827202135181061</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539237189184513</v>
+        <v>0.753830400968612</v>
       </c>
       <c r="G12" t="n">
-        <v>23.46215439802507</v>
+        <v>24.65321279107064</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68049107024875</v>
+        <v>34.67619844455614</v>
       </c>
       <c r="I12" t="n">
-        <v>2.751980866988542</v>
+        <v>2.69488788994392</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712023243240319</v>
+        <v>4.711440006053825</v>
       </c>
       <c r="K12" t="n">
-        <v>22.58177467611891</v>
+        <v>21.08808072350366</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09461735516366</v>
+        <v>42.03467605359547</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90837586967682</v>
+        <v>99.91027254515893</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.96734145132655</v>
+        <v>76.24417253139205</v>
       </c>
       <c r="C13" t="n">
-        <v>33.20506583570845</v>
+        <v>34.53593617555261</v>
       </c>
       <c r="D13" t="n">
-        <v>1.410864575431038</v>
+        <v>1.478640017808131</v>
       </c>
       <c r="E13" t="n">
-        <v>9.254796626258019</v>
+        <v>9.484093384609938</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546932767826356</v>
+        <v>0.7545712535572962</v>
       </c>
       <c r="G13" t="n">
-        <v>21.81860499780465</v>
+        <v>22.8525728911184</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71589073200123</v>
+        <v>34.71027766363562</v>
       </c>
       <c r="I13" t="n">
-        <v>2.295658263157512</v>
+        <v>2.247946985929565</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71683297989147</v>
+        <v>4.716070334733101</v>
       </c>
       <c r="K13" t="n">
-        <v>25.03265854867345</v>
+        <v>23.75582746860794</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68583170264618</v>
+        <v>41.63337835889657</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92355608702809</v>
+        <v>99.92514200305713</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.25922011816053</v>
+        <v>83.1282828209139</v>
       </c>
       <c r="C14" t="n">
-        <v>37.87207570511041</v>
+        <v>38.79619412129868</v>
       </c>
       <c r="D14" t="n">
-        <v>1.412453842867904</v>
+        <v>1.480384983934004</v>
       </c>
       <c r="E14" t="n">
-        <v>11.81604139103884</v>
+        <v>11.85619022387539</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75554340050854</v>
+        <v>0.7554617348516999</v>
       </c>
       <c r="G14" t="n">
-        <v>23.93069804449287</v>
+        <v>24.7499411718605</v>
       </c>
       <c r="H14" t="n">
-        <v>36.84251191739124</v>
+        <v>36.62163940655203</v>
       </c>
       <c r="I14" t="n">
-        <v>2.779825268682762</v>
+        <v>2.943029457017159</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722146253178372</v>
+        <v>4.721635842823124</v>
       </c>
       <c r="K14" t="n">
-        <v>17.74077988183945</v>
+        <v>16.87171717908609</v>
       </c>
       <c r="L14" t="n">
-        <v>44.29458783105925</v>
+        <v>44.23410335175052</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90744341800912</v>
+        <v>99.90201465213528</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.44237657579608</v>
+        <v>82.15837499398032</v>
       </c>
       <c r="C15" t="n">
-        <v>37.48397997941629</v>
+        <v>38.28082437884038</v>
       </c>
       <c r="D15" t="n">
-        <v>1.382715880824541</v>
+        <v>1.444122590899143</v>
       </c>
       <c r="E15" t="n">
-        <v>11.95371837481652</v>
+        <v>11.97493116108143</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562604282117925</v>
+        <v>0.7562141977557396</v>
       </c>
       <c r="G15" t="n">
-        <v>23.42685843676924</v>
+        <v>24.14368529646065</v>
       </c>
       <c r="H15" t="n">
-        <v>36.87747629095919</v>
+        <v>36.65811567512699</v>
       </c>
       <c r="I15" t="n">
-        <v>2.318719487891092</v>
+        <v>2.454967336682984</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7266276763237</v>
+        <v>4.726338735973373</v>
       </c>
       <c r="K15" t="n">
-        <v>18.55762342420393</v>
+        <v>17.84162500601969</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88117922780525</v>
+        <v>43.79579979688946</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92278263142546</v>
+        <v>99.91824918174953</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.83708324060517</v>
+        <v>79.43987633101273</v>
       </c>
       <c r="C16" t="n">
-        <v>35.23630415874941</v>
+        <v>35.94142226887979</v>
       </c>
       <c r="D16" t="n">
-        <v>1.285777829329059</v>
+        <v>1.340759186160594</v>
       </c>
       <c r="E16" t="n">
-        <v>11.43798682827238</v>
+        <v>11.45908335822245</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568787883668314</v>
+        <v>0.7568639121016844</v>
       </c>
       <c r="G16" t="n">
-        <v>21.78447185467061</v>
+        <v>22.41559549930262</v>
       </c>
       <c r="H16" t="n">
-        <v>36.90762934552354</v>
+        <v>36.68961112141736</v>
       </c>
       <c r="I16" t="n">
-        <v>1.933846167150064</v>
+        <v>2.047563803172496</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730492427292694</v>
+        <v>4.730399450635527</v>
       </c>
       <c r="K16" t="n">
-        <v>21.16291675939481</v>
+        <v>20.56012366898727</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53637020719214</v>
+        <v>43.43026052500284</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93559112533637</v>
+        <v>99.9318064628699</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.78263230106518</v>
+        <v>81.07630249183653</v>
       </c>
       <c r="C17" t="n">
-        <v>36.65596239070887</v>
+        <v>37.13689162924334</v>
       </c>
       <c r="D17" t="n">
-        <v>1.286780023601686</v>
+        <v>1.341884126485881</v>
       </c>
       <c r="E17" t="n">
-        <v>12.30028194165991</v>
+        <v>12.22154540144252</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574687344441949</v>
+        <v>0.7574989454054022</v>
       </c>
       <c r="G17" t="n">
-        <v>22.34000303103369</v>
+        <v>22.84712220921365</v>
       </c>
       <c r="H17" t="n">
-        <v>37.47494820516722</v>
+        <v>37.1331141921416</v>
       </c>
       <c r="I17" t="n">
-        <v>1.888970774882255</v>
+        <v>2.040769208363706</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734179590276216</v>
+        <v>4.734368408783764</v>
       </c>
       <c r="K17" t="n">
-        <v>19.21736769893483</v>
+        <v>18.92369750816348</v>
       </c>
       <c r="L17" t="n">
-        <v>44.0637532579877</v>
+        <v>43.87144225017872</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93708334763139</v>
+        <v>99.93203138758554</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.26000212257183</v>
+        <v>78.50631280409036</v>
       </c>
       <c r="C18" t="n">
-        <v>34.42426060431315</v>
+        <v>34.88150116262958</v>
       </c>
       <c r="D18" t="n">
-        <v>1.197231073215097</v>
+        <v>1.248070254879398</v>
       </c>
       <c r="E18" t="n">
-        <v>11.70681996050755</v>
+        <v>11.65075707785245</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579769393763595</v>
+        <v>0.7580463173752325</v>
       </c>
       <c r="G18" t="n">
-        <v>20.78532873832683</v>
+        <v>21.24983303408505</v>
       </c>
       <c r="H18" t="n">
-        <v>37.50009109575062</v>
+        <v>37.15994673888581</v>
       </c>
       <c r="I18" t="n">
-        <v>1.575198444293156</v>
+        <v>1.701869897417201</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737355871102244</v>
+        <v>4.737789483595204</v>
       </c>
       <c r="K18" t="n">
-        <v>21.73999787742813</v>
+        <v>21.49368719590965</v>
       </c>
       <c r="L18" t="n">
-        <v>43.78327010784532</v>
+        <v>43.56812360789512</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94752858958661</v>
+        <v>99.94331196643435</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.29889075506831</v>
+        <v>77.42855017436818</v>
       </c>
       <c r="C19" t="n">
-        <v>33.70244445436754</v>
+        <v>34.06043695100407</v>
       </c>
       <c r="D19" t="n">
-        <v>1.163629249102012</v>
+        <v>1.209213739655909</v>
       </c>
       <c r="E19" t="n">
-        <v>11.59757088120079</v>
+        <v>11.5253337955585</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584070564212713</v>
+        <v>0.7585109693054992</v>
       </c>
       <c r="G19" t="n">
-        <v>20.20196185450352</v>
+        <v>20.5882561256078</v>
       </c>
       <c r="H19" t="n">
-        <v>37.52137067238166</v>
+        <v>37.18272429295482</v>
       </c>
       <c r="I19" t="n">
-        <v>1.315906938826119</v>
+        <v>1.423817693126298</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740044102632942</v>
+        <v>4.740693558159371</v>
       </c>
       <c r="K19" t="n">
-        <v>22.70110924493168</v>
+        <v>22.5714498256318</v>
       </c>
       <c r="L19" t="n">
-        <v>43.55260761251212</v>
+        <v>43.3206817072066</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95616131181134</v>
+        <v>99.95256848384248</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.64612010090005</v>
+        <v>74.72033040986409</v>
       </c>
       <c r="C20" t="n">
-        <v>31.25156323967407</v>
+        <v>31.57084732300223</v>
       </c>
       <c r="D20" t="n">
-        <v>1.070508270594098</v>
+        <v>1.111526545083154</v>
       </c>
       <c r="E20" t="n">
-        <v>10.85231423784171</v>
+        <v>10.79210866896709</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587786177617802</v>
+        <v>0.7589126721487014</v>
       </c>
       <c r="G20" t="n">
-        <v>18.58527298463996</v>
+        <v>18.92501916749296</v>
       </c>
       <c r="H20" t="n">
-        <v>37.53975326872848</v>
+        <v>37.20241603990498</v>
       </c>
       <c r="I20" t="n">
-        <v>1.097126360322911</v>
+        <v>1.18714311533781</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742366361011124</v>
+        <v>4.743204200929385</v>
       </c>
       <c r="K20" t="n">
-        <v>25.35387989909994</v>
+        <v>25.27966959013592</v>
       </c>
       <c r="L20" t="n">
-        <v>43.35800389070304</v>
+        <v>43.10993259538611</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96344702947705</v>
+        <v>99.96044950852426</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.93707103242026</v>
+        <v>81.00316228787014</v>
       </c>
       <c r="C21" t="n">
-        <v>35.25786093378284</v>
+        <v>35.49850712035095</v>
       </c>
       <c r="D21" t="n">
-        <v>1.071159126463186</v>
+        <v>1.112299156842751</v>
       </c>
       <c r="E21" t="n">
-        <v>12.9786408190631</v>
+        <v>12.89720078673335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592399458339444</v>
+        <v>0.7594401852860194</v>
       </c>
       <c r="G21" t="n">
-        <v>20.47025738845617</v>
+        <v>20.75424167350217</v>
       </c>
       <c r="H21" t="n">
-        <v>39.43626176355575</v>
+        <v>39.04434299442323</v>
       </c>
       <c r="I21" t="n">
-        <v>1.476262327585952</v>
+        <v>1.689136333044993</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745249661462149</v>
+        <v>4.746501158037622</v>
       </c>
       <c r="K21" t="n">
-        <v>19.06292896757976</v>
+        <v>18.99683771212987</v>
       </c>
       <c r="L21" t="n">
-        <v>45.63003125451721</v>
+        <v>45.44838973266462</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95082115587981</v>
+        <v>99.94373456514543</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_76_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.08597471511363</v>
+        <v>45.36861109893569</v>
       </c>
       <c r="M2" t="n">
-        <v>99.6719953834978</v>
+        <v>99.48001094345463</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05808138163277</v>
+        <v>88.08061249144521</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9322808378471</v>
+        <v>45.94750774473997</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228806801814093</v>
+        <v>2.22885300737451</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710123287143928</v>
+        <v>5.720033730807481</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429356006046977</v>
+        <v>0.74295100245817</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97404262469925</v>
+        <v>33.9790959336212</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17503762781609</v>
+        <v>34.17574611307582</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583787935775351</v>
+        <v>6.590488938744483</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64334750377936</v>
+        <v>4.643443765363562</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94191861836724</v>
+        <v>11.91938750855477</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88948439721193</v>
+        <v>48.89655298068251</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636838534263</v>
+        <v>106.7634482339773</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.16035460121375</v>
+        <v>87.21644667559752</v>
       </c>
       <c r="C4" t="n">
-        <v>42.67259652492285</v>
+        <v>42.72211354435039</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185654389685337</v>
+        <v>2.187506368583017</v>
       </c>
       <c r="E4" t="n">
-        <v>6.515906034958911</v>
+        <v>6.531194529390335</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444977325868752</v>
+        <v>0.7445137523230994</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31626381326183</v>
+        <v>33.3487621245362</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24689569899626</v>
+        <v>34.24763260686257</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498026103056579</v>
+        <v>5.503626341882929</v>
       </c>
       <c r="J4" t="n">
-        <v>4.65311082866797</v>
+        <v>4.653210952019371</v>
       </c>
       <c r="K4" t="n">
-        <v>12.83964539878626</v>
+        <v>12.78355332440247</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30487507807491</v>
+        <v>44.31126399405979</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81711700178401</v>
+        <v>99.81693086281265</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.06680460062974</v>
+        <v>86.16395372932362</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43238670644458</v>
+        <v>42.52387637604247</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132555009584048</v>
+        <v>2.136567635686399</v>
       </c>
       <c r="E5" t="n">
-        <v>7.122577513731465</v>
+        <v>7.144858961710532</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745821169744045</v>
+        <v>0.7458370720521469</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50686184919837</v>
+        <v>32.57219584308807</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30777380822607</v>
+        <v>34.30850531439876</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589832939245452</v>
+        <v>4.594507202061788</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661382310900281</v>
+        <v>4.661481700325917</v>
       </c>
       <c r="K5" t="n">
-        <v>13.93319539937027</v>
+        <v>13.83604627067639</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48169494687804</v>
+        <v>43.48719884378438</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84727705269289</v>
+        <v>99.84712149050324</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.7736701405401</v>
+        <v>84.89158015360138</v>
       </c>
       <c r="C6" t="n">
-        <v>41.85215787928571</v>
+        <v>41.96521193710127</v>
       </c>
       <c r="D6" t="n">
-        <v>2.069634382433748</v>
+        <v>2.074733917674464</v>
       </c>
       <c r="E6" t="n">
-        <v>7.550864202631494</v>
+        <v>7.577168689657823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469445369646909</v>
+        <v>0.7469600447306038</v>
       </c>
       <c r="G6" t="n">
-        <v>31.54775311575534</v>
+        <v>31.62953438030504</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35944870037579</v>
+        <v>34.36016205760778</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830621846349732</v>
+        <v>3.834520784059396</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668403356029319</v>
+        <v>4.668500279566274</v>
       </c>
       <c r="K6" t="n">
-        <v>15.22632985945991</v>
+        <v>15.10841984639862</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79401690183089</v>
+        <v>42.79874301644283</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87250464057651</v>
+        <v>99.87237479994272</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.25290333241171</v>
+        <v>83.30927516843751</v>
       </c>
       <c r="C7" t="n">
-        <v>40.9264602416499</v>
+        <v>40.97866437832344</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995732266103613</v>
+        <v>1.997764221442076</v>
       </c>
       <c r="E7" t="n">
-        <v>7.81395103478104</v>
+        <v>7.829320558973946</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747900434139054</v>
+        <v>0.7479162876459056</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42125186485648</v>
+        <v>30.4561233551685</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40341997039649</v>
+        <v>34.40414923171166</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196270048765948</v>
+        <v>3.19952471570852</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674377713369088</v>
+        <v>4.67447679778691</v>
       </c>
       <c r="K7" t="n">
-        <v>16.7470966675883</v>
+        <v>16.69072483156247</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22003692836321</v>
+        <v>42.22409632389022</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8935938376014</v>
+        <v>99.89348553377613</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.97877233323811</v>
+        <v>88.03136303826541</v>
       </c>
       <c r="C8" t="n">
-        <v>43.17200840372605</v>
+        <v>43.2327598954576</v>
       </c>
       <c r="D8" t="n">
-        <v>1.999933261207812</v>
+        <v>2.001960367983711</v>
       </c>
       <c r="E8" t="n">
-        <v>9.604249551167026</v>
+        <v>9.62477690492296</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749474756564767</v>
+        <v>0.7494872269540347</v>
       </c>
       <c r="G8" t="n">
-        <v>30.90922745136616</v>
+        <v>30.9473424057403</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47583880197929</v>
+        <v>34.4764124398856</v>
       </c>
       <c r="I8" t="n">
-        <v>5.555831282423279</v>
+        <v>5.547088524316099</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684217228529794</v>
+        <v>4.684295168462717</v>
       </c>
       <c r="K8" t="n">
-        <v>12.02122766676188</v>
+        <v>11.96863696173458</v>
       </c>
       <c r="L8" t="n">
-        <v>44.62195856674607</v>
+        <v>44.6140877520559</v>
       </c>
       <c r="M8" t="n">
-        <v>99.815194637234</v>
+        <v>99.81548460924807</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.98391080341838</v>
+        <v>85.9591979096962</v>
       </c>
       <c r="C9" t="n">
-        <v>42.03966672415595</v>
+        <v>42.02183073874234</v>
       </c>
       <c r="D9" t="n">
-        <v>1.909517474794048</v>
+        <v>1.907941046967547</v>
       </c>
       <c r="E9" t="n">
-        <v>9.943077885713022</v>
+        <v>9.944574938324331</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508223738085602</v>
+        <v>0.7508331296673552</v>
       </c>
       <c r="G9" t="n">
-        <v>29.51183976765445</v>
+        <v>29.49394294450476</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53782919519377</v>
+        <v>34.53832396469834</v>
       </c>
       <c r="I9" t="n">
-        <v>4.638184269951038</v>
+        <v>4.630874825112885</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692639836303502</v>
+        <v>4.69270706042097</v>
       </c>
       <c r="K9" t="n">
-        <v>14.01608919658159</v>
+        <v>14.04080209030382</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78991543252848</v>
+        <v>43.78328137861173</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84567135326603</v>
+        <v>99.84591420765788</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.76874196241513</v>
+        <v>83.70139254972204</v>
       </c>
       <c r="C10" t="n">
-        <v>40.54428092068225</v>
+        <v>40.48266375853332</v>
       </c>
       <c r="D10" t="n">
-        <v>1.810041933961448</v>
+        <v>1.80653048678265</v>
       </c>
       <c r="E10" t="n">
-        <v>10.07028183320199</v>
+        <v>10.06016961021901</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519789365049007</v>
+        <v>0.7519888140331943</v>
       </c>
       <c r="G10" t="n">
-        <v>27.97443240657802</v>
+        <v>27.92628587207191</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59103107922543</v>
+        <v>34.59148544552694</v>
       </c>
       <c r="I10" t="n">
-        <v>3.871107419787726</v>
+        <v>3.865002233380873</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69986835315563</v>
+        <v>4.699930087707465</v>
       </c>
       <c r="K10" t="n">
-        <v>16.23125803758485</v>
+        <v>16.29860745027795</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09562258978981</v>
+        <v>43.09009337938005</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87116154805692</v>
+        <v>99.87136458819131</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.43069391658268</v>
+        <v>81.31455091164577</v>
       </c>
       <c r="C11" t="n">
-        <v>38.80634087271775</v>
+        <v>38.69493901077784</v>
       </c>
       <c r="D11" t="n">
-        <v>1.70611019259604</v>
+        <v>1.700417233406998</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03041580011631</v>
+        <v>10.00676387749447</v>
       </c>
       <c r="F11" t="n">
-        <v>0.752973251834731</v>
+        <v>0.7529829920306087</v>
       </c>
       <c r="G11" t="n">
-        <v>26.36815388939397</v>
+        <v>26.28593212755157</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63676958439762</v>
+        <v>34.63721763340801</v>
       </c>
       <c r="I11" t="n">
-        <v>3.230188374276938</v>
+        <v>3.225093347562801</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706082823967068</v>
+        <v>4.706143700191305</v>
       </c>
       <c r="K11" t="n">
-        <v>18.5693060834173</v>
+        <v>18.68544908835423</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51682228220417</v>
+        <v>42.51225072771847</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89246923833923</v>
+        <v>99.89263882685054</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.91191927649633</v>
+        <v>78.85912802150149</v>
       </c>
       <c r="C12" t="n">
-        <v>36.78751576805982</v>
+        <v>36.73860297194529</v>
       </c>
       <c r="D12" t="n">
-        <v>1.595147608722159</v>
+        <v>1.592331418870673</v>
       </c>
       <c r="E12" t="n">
-        <v>9.827202135181061</v>
+        <v>9.81913010363956</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753830400968612</v>
+        <v>0.7538393722640201</v>
       </c>
       <c r="G12" t="n">
-        <v>24.65321279107064</v>
+        <v>24.6150855088306</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67619844455614</v>
+        <v>34.67661112414493</v>
       </c>
       <c r="I12" t="n">
-        <v>2.69488788994392</v>
+        <v>2.690634417101572</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711440006053825</v>
+        <v>4.711496076650126</v>
       </c>
       <c r="K12" t="n">
-        <v>21.08808072350366</v>
+        <v>21.14087197849853</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03467605359547</v>
+        <v>42.03093912323498</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91027254515893</v>
+        <v>99.91041407367879</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.24417253139205</v>
+        <v>76.29505735830216</v>
       </c>
       <c r="C13" t="n">
-        <v>34.53593617555261</v>
+        <v>34.59001496500296</v>
       </c>
       <c r="D13" t="n">
-        <v>1.478640017808131</v>
+        <v>1.480452756852191</v>
       </c>
       <c r="E13" t="n">
-        <v>9.484093384609938</v>
+        <v>9.503294706096785</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545712535572962</v>
+        <v>0.7545785693654665</v>
       </c>
       <c r="G13" t="n">
-        <v>22.8525728911184</v>
+        <v>22.88560708520466</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71027766363562</v>
+        <v>34.71061419081147</v>
       </c>
       <c r="I13" t="n">
-        <v>2.247946985929565</v>
+        <v>2.244393991437422</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716070334733101</v>
+        <v>4.716116058534165</v>
       </c>
       <c r="K13" t="n">
-        <v>23.75582746860794</v>
+        <v>23.70494264169785</v>
       </c>
       <c r="L13" t="n">
-        <v>41.63337835889657</v>
+        <v>41.6303025483797</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92514200305713</v>
+        <v>99.92526015508051</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.1282828209139</v>
+        <v>83.30188526745587</v>
       </c>
       <c r="C14" t="n">
-        <v>38.79619412129868</v>
+        <v>39.0080743773272</v>
       </c>
       <c r="D14" t="n">
-        <v>1.480384983934004</v>
+        <v>1.482122731543662</v>
       </c>
       <c r="E14" t="n">
-        <v>11.85619022387539</v>
+        <v>11.94347258750863</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554617348516999</v>
+        <v>0.7554297462150715</v>
       </c>
       <c r="G14" t="n">
-        <v>24.7499411718605</v>
+        <v>24.87105105184629</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62163940655203</v>
+        <v>36.70939695702062</v>
       </c>
       <c r="I14" t="n">
-        <v>2.943029457017159</v>
+        <v>2.818976279477416</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721635842823124</v>
+        <v>4.721435913844196</v>
       </c>
       <c r="K14" t="n">
-        <v>16.87171717908609</v>
+        <v>16.69811473254413</v>
       </c>
       <c r="L14" t="n">
-        <v>44.23410335175052</v>
+        <v>44.19995088974696</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90201465213528</v>
+        <v>99.90613999961829</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.15837499398032</v>
+        <v>82.43337234341692</v>
       </c>
       <c r="C15" t="n">
-        <v>38.28082437884038</v>
+        <v>38.57508767633541</v>
       </c>
       <c r="D15" t="n">
-        <v>1.444122590899143</v>
+        <v>1.449887590643311</v>
       </c>
       <c r="E15" t="n">
-        <v>11.97493116108143</v>
+        <v>12.07560709965026</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562141977557396</v>
+        <v>0.7561480243980574</v>
       </c>
       <c r="G15" t="n">
-        <v>24.14368529646065</v>
+        <v>24.33012295059445</v>
       </c>
       <c r="H15" t="n">
-        <v>36.65811567512699</v>
+        <v>36.74430100875661</v>
       </c>
       <c r="I15" t="n">
-        <v>2.454967336682984</v>
+        <v>2.351380516886362</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726338735973373</v>
+        <v>4.725925152487858</v>
       </c>
       <c r="K15" t="n">
-        <v>17.84162500601969</v>
+        <v>17.56662765658312</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79579979688946</v>
+        <v>43.77997977042933</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91824918174953</v>
+        <v>99.92169510334784</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.43987633101273</v>
+        <v>79.98381364655067</v>
       </c>
       <c r="C16" t="n">
-        <v>35.94142226887979</v>
+        <v>36.48878759576519</v>
       </c>
       <c r="D16" t="n">
-        <v>1.340759186160594</v>
+        <v>1.357176657621721</v>
       </c>
       <c r="E16" t="n">
-        <v>11.45908335822245</v>
+        <v>11.63029767157721</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568639121016844</v>
+        <v>0.7567660122327476</v>
       </c>
       <c r="G16" t="n">
-        <v>22.41559549930262</v>
+        <v>22.77436896398451</v>
       </c>
       <c r="H16" t="n">
-        <v>36.68961112141736</v>
+        <v>36.77433154548344</v>
       </c>
       <c r="I16" t="n">
-        <v>2.047563803172496</v>
+        <v>1.961085219196358</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730399450635527</v>
+        <v>4.729787576454672</v>
       </c>
       <c r="K16" t="n">
-        <v>20.56012366898727</v>
+        <v>20.01618635344933</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43026052500284</v>
+        <v>43.42970992531644</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9318064628699</v>
+        <v>99.93468387453096</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.07630249183653</v>
+        <v>81.70548496053422</v>
       </c>
       <c r="C17" t="n">
-        <v>37.13689162924334</v>
+        <v>37.73968678341792</v>
       </c>
       <c r="D17" t="n">
-        <v>1.341884126485881</v>
+        <v>1.358256412143189</v>
       </c>
       <c r="E17" t="n">
-        <v>12.22154540144252</v>
+        <v>12.41308500046156</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574989454054022</v>
+        <v>0.7573680867812697</v>
       </c>
       <c r="G17" t="n">
-        <v>22.84712220921365</v>
+        <v>23.2410025554027</v>
       </c>
       <c r="H17" t="n">
-        <v>37.1331141921416</v>
+        <v>37.25210335005382</v>
       </c>
       <c r="I17" t="n">
-        <v>2.040769208363706</v>
+        <v>1.950119013308762</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734368408783764</v>
+        <v>4.733550542382934</v>
       </c>
       <c r="K17" t="n">
-        <v>18.92369750816348</v>
+        <v>18.29451503946579</v>
       </c>
       <c r="L17" t="n">
-        <v>43.87144225017872</v>
+        <v>43.90084588532059</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93203138758554</v>
+        <v>99.93504770820428</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.50631280409036</v>
+        <v>79.38963048350936</v>
       </c>
       <c r="C18" t="n">
-        <v>34.88150116262958</v>
+        <v>35.72470744072344</v>
       </c>
       <c r="D18" t="n">
-        <v>1.248070254879398</v>
+        <v>1.274139982469155</v>
       </c>
       <c r="E18" t="n">
-        <v>11.65075707785245</v>
+        <v>11.91538100823794</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580463173752325</v>
+        <v>0.7578852150394118</v>
       </c>
       <c r="G18" t="n">
-        <v>21.24983303408505</v>
+        <v>21.80169393920344</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15994673888581</v>
+        <v>37.27753895481954</v>
       </c>
       <c r="I18" t="n">
-        <v>1.701869897417201</v>
+        <v>1.626208789743559</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737789483595204</v>
+        <v>4.736782593996322</v>
       </c>
       <c r="K18" t="n">
-        <v>21.49368719590965</v>
+        <v>20.61036951649062</v>
       </c>
       <c r="L18" t="n">
-        <v>43.56812360789512</v>
+        <v>43.61075307019405</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94331196643435</v>
+        <v>99.94583002740811</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.42855017436818</v>
+        <v>78.50300431432704</v>
       </c>
       <c r="C19" t="n">
-        <v>34.06043695100407</v>
+        <v>35.08720347990881</v>
       </c>
       <c r="D19" t="n">
-        <v>1.209213739655909</v>
+        <v>1.242522792369653</v>
       </c>
       <c r="E19" t="n">
-        <v>11.5253337955585</v>
+        <v>11.84588167727718</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585109693054992</v>
+        <v>0.758321924222175</v>
       </c>
       <c r="G19" t="n">
-        <v>20.5882561256078</v>
+        <v>21.26069506054715</v>
       </c>
       <c r="H19" t="n">
-        <v>37.18272429295482</v>
+        <v>37.29901904606468</v>
       </c>
       <c r="I19" t="n">
-        <v>1.423817693126298</v>
+        <v>1.357051787457614</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740693558159371</v>
+        <v>4.739512026388593</v>
       </c>
       <c r="K19" t="n">
-        <v>22.5714498256318</v>
+        <v>21.49699568567296</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3206817072066</v>
+        <v>43.37059182520524</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95256848384248</v>
+        <v>99.95479099078702</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.72033040986409</v>
+        <v>75.99645516322929</v>
       </c>
       <c r="C20" t="n">
-        <v>31.57084732300223</v>
+        <v>32.78935171824308</v>
       </c>
       <c r="D20" t="n">
-        <v>1.111526545083154</v>
+        <v>1.152424082008697</v>
       </c>
       <c r="E20" t="n">
-        <v>10.79210866896709</v>
+        <v>11.17547749840826</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589126721487014</v>
+        <v>0.7586982549415185</v>
       </c>
       <c r="G20" t="n">
-        <v>18.92501916749296</v>
+        <v>19.71902418086885</v>
       </c>
       <c r="H20" t="n">
-        <v>37.20241603990498</v>
+        <v>37.31752934653213</v>
       </c>
       <c r="I20" t="n">
-        <v>1.18714311533781</v>
+        <v>1.131437707085322</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743204200929385</v>
+        <v>4.74186409338449</v>
       </c>
       <c r="K20" t="n">
-        <v>25.27966959013592</v>
+        <v>24.00354483677071</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10993259538611</v>
+        <v>43.16940756200128</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96044950852426</v>
+        <v>99.96230411701507</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.00316228787014</v>
+        <v>82.02031181433209</v>
       </c>
       <c r="C21" t="n">
-        <v>35.49850712035095</v>
+        <v>36.59302789725161</v>
       </c>
       <c r="D21" t="n">
-        <v>1.112299156842751</v>
+        <v>1.153151314128211</v>
       </c>
       <c r="E21" t="n">
-        <v>12.89720078673335</v>
+        <v>13.20682307423656</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594401852860194</v>
+        <v>0.7591770281194024</v>
       </c>
       <c r="G21" t="n">
-        <v>20.75424167350217</v>
+        <v>21.49696834916261</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04434299442323</v>
+        <v>39.10657897366844</v>
       </c>
       <c r="I21" t="n">
-        <v>1.689136333044993</v>
+        <v>1.552756649270601</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746501158037622</v>
+        <v>4.744856425746264</v>
       </c>
       <c r="K21" t="n">
-        <v>18.99683771212987</v>
+        <v>17.97968818566792</v>
       </c>
       <c r="L21" t="n">
-        <v>45.44838973266462</v>
+        <v>45.37555800351373</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94373456514543</v>
+        <v>99.94827408643326</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_76_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_76_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.36861109893569</v>
+        <v>44.09037007173669</v>
       </c>
       <c r="M2" t="n">
-        <v>99.48001094345463</v>
+        <v>94.12678835278609</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08061249144521</v>
+        <v>81.40854123613323</v>
       </c>
       <c r="C3" t="n">
-        <v>45.94750774473997</v>
+        <v>43.16409679168878</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22885300737451</v>
+        <v>2.176753418722936</v>
       </c>
       <c r="E3" t="n">
-        <v>5.720033730807481</v>
+        <v>4.140133957665792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74295100245817</v>
+        <v>0.7375846941036923</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9790959336212</v>
+        <v>32.7419993399575</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17574611307582</v>
+        <v>33.92889592876985</v>
       </c>
       <c r="I3" t="n">
-        <v>6.590488938744483</v>
+        <v>3.073269558765385</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643443765363562</v>
+        <v>4.609904338148077</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91938750855477</v>
+        <v>18.59145876386677</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89655298068251</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7634482339773</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.21644667559752</v>
+        <v>88.46752118962387</v>
       </c>
       <c r="C4" t="n">
-        <v>42.72211354435039</v>
+        <v>42.75410777703101</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187506368583017</v>
+        <v>2.182462941560284</v>
       </c>
       <c r="E4" t="n">
-        <v>6.531194529390335</v>
+        <v>6.514666388562687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445137523230994</v>
+        <v>0.7395193444041079</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3487621245362</v>
+        <v>33.42960113597623</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24763260686257</v>
+        <v>34.01788984258896</v>
       </c>
       <c r="I4" t="n">
-        <v>5.503626341882929</v>
+        <v>6.961385634005926</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653210952019371</v>
+        <v>4.621995902525674</v>
       </c>
       <c r="K4" t="n">
-        <v>12.78355332440247</v>
+        <v>11.53247881037611</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31126399405979</v>
+        <v>45.48197427886143</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81693086281265</v>
+        <v>99.76856086626856</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.16395372932362</v>
+        <v>87.29977356528848</v>
       </c>
       <c r="C5" t="n">
-        <v>42.52387637604247</v>
+        <v>42.66536130200205</v>
       </c>
       <c r="D5" t="n">
-        <v>2.136567635686399</v>
+        <v>2.126676001842837</v>
       </c>
       <c r="E5" t="n">
-        <v>7.144858961710532</v>
+        <v>7.317147497018146</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458370720521469</v>
+        <v>0.741161040089322</v>
       </c>
       <c r="G5" t="n">
-        <v>32.57219584308807</v>
+        <v>32.57509171552407</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30850531439876</v>
+        <v>34.09340784410882</v>
       </c>
       <c r="I5" t="n">
-        <v>4.594507202061788</v>
+        <v>5.814032966147018</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661481700325917</v>
+        <v>4.632256500558262</v>
       </c>
       <c r="K5" t="n">
-        <v>13.83604627067639</v>
+        <v>12.70022643471153</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48719884378438</v>
+        <v>44.44104044011958</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84712149050324</v>
+        <v>99.80662817683316</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.89158015360138</v>
+        <v>85.8428927353122</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96521193710127</v>
+        <v>42.11070000312963</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074733917674464</v>
+        <v>2.056809428560814</v>
       </c>
       <c r="E6" t="n">
-        <v>7.577168689657823</v>
+        <v>7.885787725720554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469600447306038</v>
+        <v>0.7425580550552686</v>
       </c>
       <c r="G6" t="n">
-        <v>31.62953438030504</v>
+        <v>31.50491928185805</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36016205760778</v>
+        <v>34.15767053254235</v>
       </c>
       <c r="I6" t="n">
-        <v>3.834520784059396</v>
+        <v>4.854159867479727</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668500279566274</v>
+        <v>4.640987844095428</v>
       </c>
       <c r="K6" t="n">
-        <v>15.10841984639862</v>
+        <v>14.15710726468781</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79874301644283</v>
+        <v>43.57069181645626</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87237479994272</v>
+        <v>99.83849908427369</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.30927516843751</v>
+        <v>84.22169790397973</v>
       </c>
       <c r="C7" t="n">
-        <v>40.97866437832344</v>
+        <v>41.24306853034554</v>
       </c>
       <c r="D7" t="n">
-        <v>1.997764221442076</v>
+        <v>1.979527753731159</v>
       </c>
       <c r="E7" t="n">
-        <v>7.829320558973946</v>
+        <v>8.264760490112163</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479162876459056</v>
+        <v>0.7437487865812945</v>
       </c>
       <c r="G7" t="n">
-        <v>30.4561233551685</v>
+        <v>30.32116696447456</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40414923171166</v>
+        <v>34.21244418273955</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19952471570852</v>
+        <v>4.051619810207916</v>
       </c>
       <c r="J7" t="n">
-        <v>4.67447679778691</v>
+        <v>4.64842991613309</v>
       </c>
       <c r="K7" t="n">
-        <v>16.69072483156247</v>
+        <v>15.77830209602026</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22409632389022</v>
+        <v>42.84379159953755</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89348553377613</v>
+        <v>99.86516222590336</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.03136303826541</v>
+        <v>82.35893203568168</v>
       </c>
       <c r="C8" t="n">
-        <v>43.2327598954576</v>
+        <v>40.00916310024108</v>
       </c>
       <c r="D8" t="n">
-        <v>2.001960367983711</v>
+        <v>1.891212207471539</v>
       </c>
       <c r="E8" t="n">
-        <v>9.62477690492296</v>
+        <v>8.459527728564913</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494872269540347</v>
+        <v>0.7447665237278889</v>
       </c>
       <c r="G8" t="n">
-        <v>30.9473424057403</v>
+        <v>28.96840471163453</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4764124398856</v>
+        <v>34.25926009148289</v>
       </c>
       <c r="I8" t="n">
-        <v>5.547088524316099</v>
+        <v>3.380969999500602</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684295168462717</v>
+        <v>4.654790773299305</v>
       </c>
       <c r="K8" t="n">
-        <v>11.96863696173458</v>
+        <v>17.64106796431834</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6140877520559</v>
+        <v>42.23722394071257</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81548460924807</v>
+        <v>99.88745500527199</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.9591979096962</v>
+        <v>80.33616808392604</v>
       </c>
       <c r="C9" t="n">
-        <v>42.02183073874234</v>
+        <v>38.51072638624056</v>
       </c>
       <c r="D9" t="n">
-        <v>1.907941046967547</v>
+        <v>1.796018859561764</v>
       </c>
       <c r="E9" t="n">
-        <v>9.944574938324331</v>
+        <v>8.50384982561221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508331296673552</v>
+        <v>0.7456382012636327</v>
       </c>
       <c r="G9" t="n">
-        <v>29.49394294450476</v>
+        <v>27.51029259856153</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53832396469834</v>
+        <v>34.2993572581271</v>
       </c>
       <c r="I9" t="n">
-        <v>4.630874825112885</v>
+        <v>2.820772582902113</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69270706042097</v>
+        <v>4.660238757897704</v>
       </c>
       <c r="K9" t="n">
-        <v>14.04080209030382</v>
+        <v>19.66383191607395</v>
       </c>
       <c r="L9" t="n">
-        <v>43.78328137861173</v>
+        <v>41.73152586436603</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84591420765788</v>
+        <v>99.90608416668053</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.70139254972204</v>
+        <v>85.52162664423496</v>
       </c>
       <c r="C10" t="n">
-        <v>40.48266375853332</v>
+        <v>41.93779908566658</v>
       </c>
       <c r="D10" t="n">
-        <v>1.80653048678265</v>
+        <v>1.798182870340581</v>
       </c>
       <c r="E10" t="n">
-        <v>10.06016961021901</v>
+        <v>10.46474438044608</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519888140331943</v>
+        <v>0.7465366156071357</v>
       </c>
       <c r="G10" t="n">
-        <v>27.92628587207191</v>
+        <v>28.97886578512853</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59148544552694</v>
+        <v>35.77611054203727</v>
       </c>
       <c r="I10" t="n">
-        <v>3.865002233380873</v>
+        <v>3.091332603130786</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699930087707465</v>
+        <v>4.665853847544597</v>
       </c>
       <c r="K10" t="n">
-        <v>16.29860745027795</v>
+        <v>14.47837335576505</v>
       </c>
       <c r="L10" t="n">
-        <v>43.09009337938005</v>
+        <v>43.480907146561</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87136458819131</v>
+        <v>99.89707958799262</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.31455091164577</v>
+        <v>85.15554274279836</v>
       </c>
       <c r="C11" t="n">
-        <v>38.69493901077784</v>
+        <v>41.96712874617025</v>
       </c>
       <c r="D11" t="n">
-        <v>1.700417233406998</v>
+        <v>1.77573719452475</v>
       </c>
       <c r="E11" t="n">
-        <v>10.00676387749447</v>
+        <v>10.81965552869259</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529829920306087</v>
+        <v>0.7472999024556396</v>
       </c>
       <c r="G11" t="n">
-        <v>26.28593212755157</v>
+        <v>28.66734487644004</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63721763340801</v>
+        <v>35.86289486757605</v>
       </c>
       <c r="I11" t="n">
-        <v>3.225093347562801</v>
+        <v>2.611985982761544</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706143700191305</v>
+        <v>4.670624390347747</v>
       </c>
       <c r="K11" t="n">
-        <v>18.68544908835423</v>
+        <v>14.84445725720164</v>
       </c>
       <c r="L11" t="n">
-        <v>42.51225072771847</v>
+        <v>43.10143672600462</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89263882685054</v>
+        <v>99.91302272937651</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.85912802150149</v>
+        <v>83.13316210700401</v>
       </c>
       <c r="C12" t="n">
-        <v>36.73860297194529</v>
+        <v>40.35043269725777</v>
       </c>
       <c r="D12" t="n">
-        <v>1.592331418870673</v>
+        <v>1.690179393383105</v>
       </c>
       <c r="E12" t="n">
-        <v>9.81913010363956</v>
+        <v>10.66144029086118</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538393722640201</v>
+        <v>0.747952684449557</v>
       </c>
       <c r="G12" t="n">
-        <v>24.6150855088306</v>
+        <v>27.28610727001941</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67661112414493</v>
+        <v>35.89422185148489</v>
       </c>
       <c r="I12" t="n">
-        <v>2.690634417101572</v>
+        <v>2.178556338996134</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711496076650126</v>
+        <v>4.674704277809731</v>
       </c>
       <c r="K12" t="n">
-        <v>21.14087197849853</v>
+        <v>16.86683789299599</v>
       </c>
       <c r="L12" t="n">
-        <v>42.03093912323498</v>
+        <v>42.71017424355842</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91041407367879</v>
+        <v>99.92744483381217</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.29505735830216</v>
+        <v>84.38504750955137</v>
       </c>
       <c r="C13" t="n">
-        <v>34.59001496500296</v>
+        <v>41.37258005464808</v>
       </c>
       <c r="D13" t="n">
-        <v>1.480452756852191</v>
+        <v>1.691551000219931</v>
       </c>
       <c r="E13" t="n">
-        <v>9.503294706096785</v>
+        <v>11.33514230848267</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545785693654665</v>
+        <v>0.7485596596733883</v>
       </c>
       <c r="G13" t="n">
-        <v>22.88560708520466</v>
+        <v>27.63090157776232</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71061419081147</v>
+        <v>36.24600177794872</v>
       </c>
       <c r="I13" t="n">
-        <v>2.244393991437422</v>
+        <v>2.054393312505668</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716116058534165</v>
+        <v>4.678497872958677</v>
       </c>
       <c r="K13" t="n">
-        <v>23.70494264169785</v>
+        <v>15.61495249044862</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6303025483797</v>
+        <v>42.9440432051615</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92526015508051</v>
+        <v>99.9315757502582</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.30188526745587</v>
+        <v>82.39917807087797</v>
       </c>
       <c r="C14" t="n">
-        <v>39.0080743773272</v>
+        <v>39.70561751197958</v>
       </c>
       <c r="D14" t="n">
-        <v>1.482122731543662</v>
+        <v>1.610044358848807</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94347258750863</v>
+        <v>11.07449361071123</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554297462150715</v>
+        <v>0.7490784424043458</v>
       </c>
       <c r="G14" t="n">
-        <v>24.87105105184629</v>
+        <v>26.29951873127014</v>
       </c>
       <c r="H14" t="n">
-        <v>36.70939695702062</v>
+        <v>36.27112175275054</v>
       </c>
       <c r="I14" t="n">
-        <v>2.818976279477416</v>
+        <v>1.713180909865737</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721435913844196</v>
+        <v>4.681740265027162</v>
       </c>
       <c r="K14" t="n">
-        <v>16.69811473254413</v>
+        <v>17.60082192912203</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19995088974696</v>
+        <v>42.63649407799546</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90613999961829</v>
+        <v>99.94293351909708</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.43337234341692</v>
+        <v>81.53728212636561</v>
       </c>
       <c r="C15" t="n">
-        <v>38.57508767633541</v>
+        <v>39.09054851116325</v>
       </c>
       <c r="D15" t="n">
-        <v>1.449887590643311</v>
+        <v>1.57448489210413</v>
       </c>
       <c r="E15" t="n">
-        <v>12.07560709965026</v>
+        <v>11.07099167719535</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561480243980574</v>
+        <v>0.7495214175836987</v>
       </c>
       <c r="G15" t="n">
-        <v>24.33012295059445</v>
+        <v>25.7186671189616</v>
       </c>
       <c r="H15" t="n">
-        <v>36.74430100875661</v>
+        <v>36.29257105065341</v>
       </c>
       <c r="I15" t="n">
-        <v>2.351380516886362</v>
+        <v>1.446537109969298</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725925152487858</v>
+        <v>4.684508859898117</v>
       </c>
       <c r="K15" t="n">
-        <v>17.56662765658312</v>
+        <v>18.46271787363439</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77997977042933</v>
+        <v>42.39854420883381</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92169510334784</v>
+        <v>99.95181059363145</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.98381364655067</v>
+        <v>79.17672867636642</v>
       </c>
       <c r="C16" t="n">
-        <v>36.48878759576519</v>
+        <v>36.95401958778576</v>
       </c>
       <c r="D16" t="n">
-        <v>1.357176657621721</v>
+        <v>1.478356775935088</v>
       </c>
       <c r="E16" t="n">
-        <v>11.63029767157721</v>
+        <v>10.59607670058457</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567660122327476</v>
+        <v>0.749901987127074</v>
       </c>
       <c r="G16" t="n">
-        <v>22.77436896398451</v>
+        <v>24.14844752973422</v>
       </c>
       <c r="H16" t="n">
-        <v>36.77433154548344</v>
+        <v>36.3109986057154</v>
       </c>
       <c r="I16" t="n">
-        <v>1.961085219196358</v>
+        <v>1.206059657725854</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729787576454672</v>
+        <v>4.686887419544213</v>
       </c>
       <c r="K16" t="n">
-        <v>20.01618635344933</v>
+        <v>20.82327132363359</v>
       </c>
       <c r="L16" t="n">
-        <v>43.42970992531644</v>
+        <v>42.18252750219261</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93468387453096</v>
+        <v>99.95981841361196</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.70548496053422</v>
+        <v>84.1247076533392</v>
       </c>
       <c r="C17" t="n">
-        <v>37.73968678341792</v>
+        <v>40.15095396831221</v>
       </c>
       <c r="D17" t="n">
-        <v>1.358256412143189</v>
+        <v>1.479212375102822</v>
       </c>
       <c r="E17" t="n">
-        <v>12.41308500046156</v>
+        <v>12.31393231469404</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573680867812697</v>
+        <v>0.7503359929952866</v>
       </c>
       <c r="G17" t="n">
-        <v>23.2410025554027</v>
+        <v>25.6307106551173</v>
       </c>
       <c r="H17" t="n">
-        <v>37.25210335005382</v>
+        <v>37.80030080904471</v>
       </c>
       <c r="I17" t="n">
-        <v>1.950119013308762</v>
+        <v>1.460615550164487</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733550542382934</v>
+        <v>4.689599956220542</v>
       </c>
       <c r="K17" t="n">
-        <v>18.29451503946579</v>
+        <v>15.87529234666079</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90084588532059</v>
+        <v>43.92509466143747</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93504770820428</v>
+        <v>99.95134097641048</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.38963048350936</v>
+        <v>85.79200977946155</v>
       </c>
       <c r="C18" t="n">
-        <v>35.72470744072344</v>
+        <v>40.91948412345448</v>
       </c>
       <c r="D18" t="n">
-        <v>1.274139982469155</v>
+        <v>1.480538751906092</v>
       </c>
       <c r="E18" t="n">
-        <v>11.91538100823794</v>
+        <v>12.95049430076659</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578852150394118</v>
+        <v>0.7510088025745727</v>
       </c>
       <c r="G18" t="n">
-        <v>21.80169393920344</v>
+        <v>25.77413385858103</v>
       </c>
       <c r="H18" t="n">
-        <v>37.27753895481954</v>
+        <v>37.83419549718661</v>
       </c>
       <c r="I18" t="n">
-        <v>1.626208789743559</v>
+        <v>2.307833552355593</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736782593996322</v>
+        <v>4.69380501609108</v>
       </c>
       <c r="K18" t="n">
-        <v>20.61036951649062</v>
+        <v>14.20799022053843</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61075307019405</v>
+        <v>44.79566678856379</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94583002740811</v>
+        <v>99.92314113255671</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.50300431432704</v>
+        <v>83.1320920020064</v>
       </c>
       <c r="C19" t="n">
-        <v>35.08720347990881</v>
+        <v>38.61679037420026</v>
       </c>
       <c r="D19" t="n">
-        <v>1.242522792369653</v>
+        <v>1.383655364765223</v>
       </c>
       <c r="E19" t="n">
-        <v>11.84588167727718</v>
+        <v>12.42382060082561</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758321924222175</v>
+        <v>0.7515883824953524</v>
       </c>
       <c r="G19" t="n">
-        <v>21.26069506054715</v>
+        <v>24.08752796216212</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29901904606468</v>
+        <v>37.86339347722872</v>
       </c>
       <c r="I19" t="n">
-        <v>1.357051787457614</v>
+        <v>1.924678823933413</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739512026388593</v>
+        <v>4.697427390595953</v>
       </c>
       <c r="K19" t="n">
-        <v>21.49699568567296</v>
+        <v>16.86790799799362</v>
       </c>
       <c r="L19" t="n">
-        <v>43.37059182520524</v>
+        <v>44.45119514024069</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95479099078702</v>
+        <v>99.93589351243456</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.99645516322929</v>
+        <v>80.3947536005943</v>
       </c>
       <c r="C20" t="n">
-        <v>32.78935171824308</v>
+        <v>36.1765704121603</v>
       </c>
       <c r="D20" t="n">
-        <v>1.152424082008697</v>
+        <v>1.284561528682622</v>
       </c>
       <c r="E20" t="n">
-        <v>11.17547749840826</v>
+        <v>11.8015529345538</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586982549415185</v>
+        <v>0.7520885287528936</v>
       </c>
       <c r="G20" t="n">
-        <v>19.71902418086885</v>
+        <v>22.36244120407148</v>
       </c>
       <c r="H20" t="n">
-        <v>37.31752934653213</v>
+        <v>37.88858976150679</v>
       </c>
       <c r="I20" t="n">
-        <v>1.131437707085322</v>
+        <v>1.604966338321141</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74186409338449</v>
+        <v>4.700553304705585</v>
       </c>
       <c r="K20" t="n">
-        <v>24.00354483677071</v>
+        <v>19.6052463994057</v>
       </c>
       <c r="L20" t="n">
-        <v>43.16940756200128</v>
+        <v>44.16471988776919</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96230411701507</v>
+        <v>99.94653669933518</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.02031181433209</v>
+        <v>77.62402595976079</v>
       </c>
       <c r="C21" t="n">
-        <v>36.59302789725161</v>
+        <v>33.65282854666077</v>
       </c>
       <c r="D21" t="n">
-        <v>1.153151314128211</v>
+        <v>1.184838213419029</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20682307423656</v>
+        <v>11.10841271293187</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591770281194024</v>
+        <v>0.7525207297174332</v>
       </c>
       <c r="G21" t="n">
-        <v>21.49696834916261</v>
+        <v>20.62639608325566</v>
       </c>
       <c r="H21" t="n">
-        <v>39.10657897366844</v>
+        <v>37.91036310920978</v>
       </c>
       <c r="I21" t="n">
-        <v>1.552756649270601</v>
+        <v>1.338240550493056</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744856425746264</v>
+        <v>4.703254560733958</v>
       </c>
       <c r="K21" t="n">
-        <v>17.97968818566792</v>
+        <v>22.37597404023922</v>
       </c>
       <c r="L21" t="n">
-        <v>45.37555800351373</v>
+        <v>43.92661501481332</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94827408643326</v>
+        <v>99.95541760171331</v>
       </c>
     </row>
   </sheetData>
